--- a/artfynd/A 24466-2026 artfynd.xlsx
+++ b/artfynd/A 24466-2026 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>128976602</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -780,11 +780,11 @@
         <v>128976921</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
